--- a/data/target_dispatch/우체국택배_파보겔_87건_일괄접수.xlsx
+++ b/data/target_dispatch/우체국택배_파보겔_87건_일괄접수.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="423">
   <si>
     <t>받는 분 이름</t>
   </si>
@@ -298,6 +298,75 @@
     <t>디어마이펫</t>
   </si>
   <si>
+    <t>댕냥구리 강아지분양 고양이분양 구리본점(심우남)</t>
+  </si>
+  <si>
+    <t>Parachiwo pom(유지혜)</t>
+  </si>
+  <si>
+    <t>삼성켄넬(김성학)</t>
+  </si>
+  <si>
+    <t>더조은 펫타운1.2.3.4.5동(박명규외 3인)</t>
+  </si>
+  <si>
+    <t>허니펫(강동규)</t>
+  </si>
+  <si>
+    <t>멍스펫(설수진)</t>
+  </si>
+  <si>
+    <t>캣츠비(한병현)</t>
+  </si>
+  <si>
+    <t>펫샵/비비냥(염주빈)</t>
+  </si>
+  <si>
+    <t>경남고성군 거류면동해로447-15(함금순)</t>
+  </si>
+  <si>
+    <t>폼스홀릭(임희진)</t>
+  </si>
+  <si>
+    <t>댕구르냥(박현구)</t>
+  </si>
+  <si>
+    <t>캣독365 청주점 강아지분양 고양이분양(현가영)</t>
+  </si>
+  <si>
+    <t>보듬캣(이아름)</t>
+  </si>
+  <si>
+    <t>코코캔넬(심형진)</t>
+  </si>
+  <si>
+    <t>티니리안(박태순)</t>
+  </si>
+  <si>
+    <t>도그하우스 대구점(이성욱)</t>
+  </si>
+  <si>
+    <t>대성독하우스(신용성)</t>
+  </si>
+  <si>
+    <t>박달농장(조상국)</t>
+  </si>
+  <si>
+    <t>포근하개도그하우스(김형욱)</t>
+  </si>
+  <si>
+    <t>지예</t>
+  </si>
+  <si>
+    <t>지용주</t>
+  </si>
+  <si>
+    <t>머머켄넬</t>
+  </si>
+  <si>
+    <t>이정훈강아지 하남본점(이경표)</t>
+  </si>
+  <si>
     <t>원주시 태장동 흥양로30</t>
   </si>
   <si>
@@ -559,6 +628,75 @@
     <t>인천광역시 연수구 먼우금로 197,</t>
   </si>
   <si>
+    <t>경기도 구리시 검배로6번길 8</t>
+  </si>
+  <si>
+    <t>전남 나주시 금천면 신가신촌길</t>
+  </si>
+  <si>
+    <t>인천시 강화군 불은면 불은북로</t>
+  </si>
+  <si>
+    <t>평창읍종부1길 211-27</t>
+  </si>
+  <si>
+    <t>경기도 김포시 대곶북로9</t>
+  </si>
+  <si>
+    <t>충북 음성군 금왕읍 대금로</t>
+  </si>
+  <si>
+    <t>고창군고창읍 덕산리 966-1 캣츠비</t>
+  </si>
+  <si>
+    <t>광주 북구 면앙로 14</t>
+  </si>
+  <si>
+    <t>경남 고성군 거류면 동해로</t>
+  </si>
+  <si>
+    <t>도창동 114-5 애견</t>
+  </si>
+  <si>
+    <t>경기도 남양주시 경춘로1286번안길 27</t>
+  </si>
+  <si>
+    <t>충북 청주시 율량동 1977</t>
+  </si>
+  <si>
+    <t>경기도 이천시 창전동 167-1</t>
+  </si>
+  <si>
+    <t>고령군 운수면 잣밭길</t>
+  </si>
+  <si>
+    <t>경북 김천시 감문면 문화로</t>
+  </si>
+  <si>
+    <t>대구 북구 태전동246-9 1층</t>
+  </si>
+  <si>
+    <t>경북포항시북구청하면용산길209 ~64</t>
+  </si>
+  <si>
+    <t>경북 경주시 내남면</t>
+  </si>
+  <si>
+    <t>경북포항시 북구 장량로31번길51 1층</t>
+  </si>
+  <si>
+    <t>경기도 포천시 영중면 호국로</t>
+  </si>
+  <si>
+    <t>충남 서천군 마산면 삼일로</t>
+  </si>
+  <si>
+    <t>충북 옥천군 안남면 중봉</t>
+  </si>
+  <si>
+    <t>경기도 하남시 망월동 1098</t>
+  </si>
+  <si>
     <t>대흥아파트202-1202</t>
   </si>
   <si>
@@ -757,6 +895,63 @@
     <t>114호</t>
   </si>
   <si>
+    <t>댕냥구리</t>
+  </si>
+  <si>
+    <t>9-11</t>
+  </si>
+  <si>
+    <t>430 2층</t>
+  </si>
+  <si>
+    <t>202호</t>
+  </si>
+  <si>
+    <t>1499 1층 멍스펫</t>
+  </si>
+  <si>
+    <t>맨안쪽</t>
+  </si>
+  <si>
+    <t>. 1층</t>
+  </si>
+  <si>
+    <t>447-15</t>
+  </si>
+  <si>
+    <t>캣독365</t>
+  </si>
+  <si>
+    <t>오구은광빌딩 2층 고양이</t>
+  </si>
+  <si>
+    <t>213-45</t>
+  </si>
+  <si>
+    <t>144-8번지</t>
+  </si>
+  <si>
+    <t>도그하우스</t>
+  </si>
+  <si>
+    <t>박달로348-59</t>
+  </si>
+  <si>
+    <t>102호 포근하개</t>
+  </si>
+  <si>
+    <t>3344</t>
+  </si>
+  <si>
+    <t>493번길 81-20</t>
+  </si>
+  <si>
+    <t>213-34</t>
+  </si>
+  <si>
+    <t>203-1 이정훈강아지</t>
+  </si>
+  <si>
     <t>010-3114-1100</t>
   </si>
   <si>
@@ -1012,10 +1207,76 @@
     <t>010-2982-6849</t>
   </si>
   <si>
-    <t>010-5407-5708</t>
+    <t>010-3848-5709</t>
   </si>
   <si>
     <t>010-8433-6449</t>
+  </si>
+  <si>
+    <t>010-7535-6488</t>
+  </si>
+  <si>
+    <t>010-7575-1231</t>
+  </si>
+  <si>
+    <t>010-5544-5008</t>
+  </si>
+  <si>
+    <t>010-3228-1333</t>
+  </si>
+  <si>
+    <t>010-6616-6919</t>
+  </si>
+  <si>
+    <t>010-5757-6766</t>
+  </si>
+  <si>
+    <t>010-5667-3733</t>
+  </si>
+  <si>
+    <t>010-2987-5256</t>
+  </si>
+  <si>
+    <t>010-2481-4481</t>
+  </si>
+  <si>
+    <t>010-9022-3590</t>
+  </si>
+  <si>
+    <t>010-8112-6192</t>
+  </si>
+  <si>
+    <t>010-4338-3264</t>
+  </si>
+  <si>
+    <t>010-9268-1937</t>
+  </si>
+  <si>
+    <t>010-9324-5524</t>
+  </si>
+  <si>
+    <t>010-4521-1831</t>
+  </si>
+  <si>
+    <t>010-3933-1402</t>
+  </si>
+  <si>
+    <t>010-9065-5805</t>
+  </si>
+  <si>
+    <t>010-7712-7003</t>
+  </si>
+  <si>
+    <t>010-9362-3587</t>
+  </si>
+  <si>
+    <t>010-3036-6023</t>
+  </si>
+  <si>
+    <t>010-8574-3998</t>
+  </si>
+  <si>
+    <t>010-2913-7457</t>
   </si>
   <si>
     <t>파보겔 샘플 1병 (배송전 연락바랍니다)</t>
@@ -1353,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1384,16 +1645,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="F2" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="G2" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1401,16 +1662,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="F3" t="s">
-        <v>248</v>
+        <v>313</v>
       </c>
       <c r="G3" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1418,16 +1679,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>229</v>
       </c>
       <c r="F4" t="s">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="G4" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1435,16 +1696,16 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F5" t="s">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="G5" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1452,16 +1713,16 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="F6" t="s">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="G6" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1469,16 +1730,16 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="F7" t="s">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="G7" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1486,16 +1747,16 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>318</v>
       </c>
       <c r="G8" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1503,16 +1764,16 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="F9" t="s">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="G9" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1520,16 +1781,16 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>189</v>
+        <v>235</v>
       </c>
       <c r="F10" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="G10" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1537,16 +1798,16 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D11" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="F11" t="s">
-        <v>256</v>
+        <v>321</v>
       </c>
       <c r="G11" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1554,16 +1815,16 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="F12" t="s">
-        <v>257</v>
+        <v>322</v>
       </c>
       <c r="G12" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1571,16 +1832,16 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F13" t="s">
-        <v>258</v>
+        <v>323</v>
       </c>
       <c r="G13" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1588,16 +1849,16 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="F14" t="s">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="G14" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1605,16 +1866,16 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="F15" t="s">
-        <v>260</v>
+        <v>325</v>
       </c>
       <c r="G15" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1622,16 +1883,16 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="F16" t="s">
-        <v>261</v>
+        <v>326</v>
       </c>
       <c r="G16" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1639,16 +1900,16 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="F17" t="s">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="G17" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1656,16 +1917,16 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F18" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
       <c r="G18" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1673,16 +1934,16 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
-        <v>196</v>
+        <v>242</v>
       </c>
       <c r="F19" t="s">
-        <v>264</v>
+        <v>329</v>
       </c>
       <c r="G19" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1690,16 +1951,16 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>197</v>
+        <v>243</v>
       </c>
       <c r="F20" t="s">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="G20" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1707,16 +1968,16 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="F21" t="s">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="G21" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1724,16 +1985,16 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="F22" t="s">
-        <v>267</v>
+        <v>332</v>
       </c>
       <c r="G22" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1741,16 +2002,16 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="F23" t="s">
-        <v>268</v>
+        <v>333</v>
       </c>
       <c r="G23" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1758,16 +2019,16 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F24" t="s">
-        <v>269</v>
+        <v>334</v>
       </c>
       <c r="G24" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1775,16 +2036,16 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="F25" t="s">
-        <v>270</v>
+        <v>335</v>
       </c>
       <c r="G25" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1792,16 +2053,16 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="F26" t="s">
-        <v>271</v>
+        <v>336</v>
       </c>
       <c r="G26" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1809,16 +2070,16 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="D27" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F27" t="s">
-        <v>272</v>
+        <v>337</v>
       </c>
       <c r="G27" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1826,16 +2087,16 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="D28" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F28" t="s">
-        <v>273</v>
+        <v>338</v>
       </c>
       <c r="G28" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1843,16 +2104,16 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="F29" t="s">
-        <v>274</v>
+        <v>339</v>
       </c>
       <c r="G29" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1860,16 +2121,16 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="D30" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F30" t="s">
-        <v>275</v>
+        <v>340</v>
       </c>
       <c r="G30" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1877,16 +2138,16 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F31" t="s">
-        <v>276</v>
+        <v>341</v>
       </c>
       <c r="G31" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1894,16 +2155,16 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s">
-        <v>204</v>
+        <v>250</v>
       </c>
       <c r="F32" t="s">
-        <v>277</v>
+        <v>342</v>
       </c>
       <c r="G32" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1911,16 +2172,16 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="D33" t="s">
-        <v>205</v>
+        <v>251</v>
       </c>
       <c r="F33" t="s">
-        <v>278</v>
+        <v>343</v>
       </c>
       <c r="G33" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1928,16 +2189,16 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="F34" t="s">
-        <v>279</v>
+        <v>344</v>
       </c>
       <c r="G34" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1945,16 +2206,16 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="F35" t="s">
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="G35" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1962,16 +2223,16 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="D36" t="s">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="F36" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="G36" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1979,16 +2240,16 @@
         <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="D37" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="F37" t="s">
-        <v>282</v>
+        <v>347</v>
       </c>
       <c r="G37" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1996,16 +2257,16 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D38" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F38" t="s">
-        <v>283</v>
+        <v>348</v>
       </c>
       <c r="G38" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2013,16 +2274,16 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D39" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F39" t="s">
-        <v>284</v>
+        <v>349</v>
       </c>
       <c r="G39" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2030,16 +2291,16 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="D40" t="s">
-        <v>210</v>
+        <v>256</v>
       </c>
       <c r="F40" t="s">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="G40" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2047,16 +2308,16 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="D41" t="s">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="F41" t="s">
-        <v>286</v>
+        <v>351</v>
       </c>
       <c r="G41" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2064,16 +2325,16 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="D42" t="s">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="F42" t="s">
-        <v>287</v>
+        <v>352</v>
       </c>
       <c r="G42" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2081,16 +2342,16 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="D43" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="F43" t="s">
-        <v>288</v>
+        <v>353</v>
       </c>
       <c r="G43" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2098,16 +2359,16 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="F44" t="s">
-        <v>289</v>
+        <v>354</v>
       </c>
       <c r="G44" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2115,16 +2376,16 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="F45" t="s">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="G45" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2132,16 +2393,16 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="F46" t="s">
-        <v>291</v>
+        <v>356</v>
       </c>
       <c r="G46" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2149,16 +2410,16 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="D47" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F47" t="s">
-        <v>292</v>
+        <v>357</v>
       </c>
       <c r="G47" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2166,16 +2427,16 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="D48" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="F48" t="s">
-        <v>293</v>
+        <v>358</v>
       </c>
       <c r="G48" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2183,16 +2444,16 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="D49" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="F49" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="G49" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2200,16 +2461,16 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="D50" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="F50" t="s">
-        <v>295</v>
+        <v>360</v>
       </c>
       <c r="G50" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2217,16 +2478,16 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D51" t="s">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="F51" t="s">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="G51" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2234,16 +2495,16 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="D52" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="F52" t="s">
-        <v>297</v>
+        <v>362</v>
       </c>
       <c r="G52" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2251,16 +2512,16 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D53" t="s">
-        <v>205</v>
+        <v>251</v>
       </c>
       <c r="F53" t="s">
-        <v>298</v>
+        <v>363</v>
       </c>
       <c r="G53" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2268,16 +2529,16 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="D54" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F54" t="s">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="G54" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2285,16 +2546,16 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="D55" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="F55" t="s">
-        <v>300</v>
+        <v>365</v>
       </c>
       <c r="G55" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2302,16 +2563,16 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="D56" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F56" t="s">
-        <v>301</v>
+        <v>366</v>
       </c>
       <c r="G56" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2319,16 +2580,16 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D57" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="F57" t="s">
-        <v>302</v>
+        <v>367</v>
       </c>
       <c r="G57" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2336,16 +2597,16 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="D58" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="F58" t="s">
-        <v>303</v>
+        <v>368</v>
       </c>
       <c r="G58" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2353,16 +2614,16 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="D59" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="F59" t="s">
-        <v>304</v>
+        <v>369</v>
       </c>
       <c r="G59" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2370,16 +2631,16 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="D60" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="F60" t="s">
-        <v>305</v>
+        <v>370</v>
       </c>
       <c r="G60" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2387,16 +2648,16 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="D61" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="F61" t="s">
-        <v>306</v>
+        <v>371</v>
       </c>
       <c r="G61" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2404,16 +2665,16 @@
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="D62" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F62" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="G62" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2421,16 +2682,16 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="D63" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F63" t="s">
-        <v>308</v>
+        <v>373</v>
       </c>
       <c r="G63" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2438,16 +2699,16 @@
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D64" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="F64" t="s">
-        <v>309</v>
+        <v>374</v>
       </c>
       <c r="G64" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2455,16 +2716,16 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="D65" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="F65" t="s">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="G65" t="s">
-        <v>335</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2472,16 +2733,16 @@
         <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="F66" t="s">
-        <v>311</v>
+        <v>376</v>
       </c>
       <c r="G66" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2489,16 +2750,16 @@
         <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D67" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F67" t="s">
-        <v>312</v>
+        <v>377</v>
       </c>
       <c r="G67" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2506,16 +2767,16 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="D68" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F68" t="s">
-        <v>313</v>
+        <v>378</v>
       </c>
       <c r="G68" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2523,16 +2784,16 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="D69" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F69" t="s">
-        <v>314</v>
+        <v>379</v>
       </c>
       <c r="G69" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2540,16 +2801,16 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="D70" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="F70" t="s">
-        <v>315</v>
+        <v>380</v>
       </c>
       <c r="G70" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2557,16 +2818,16 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="D71" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="F71" t="s">
-        <v>316</v>
+        <v>381</v>
       </c>
       <c r="G71" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2574,16 +2835,16 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="D72" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F72" t="s">
-        <v>317</v>
+        <v>382</v>
       </c>
       <c r="G72" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2591,16 +2852,16 @@
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="D73" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="F73" t="s">
-        <v>318</v>
+        <v>383</v>
       </c>
       <c r="G73" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2608,16 +2869,16 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="D74" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="F74" t="s">
-        <v>319</v>
+        <v>384</v>
       </c>
       <c r="G74" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2625,16 +2886,16 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="D75" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F75" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="G75" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2642,16 +2903,16 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="D76" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="F76" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="G76" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2659,16 +2920,16 @@
         <v>82</v>
       </c>
       <c r="C77" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="D77" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="F77" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="G77" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2676,16 +2937,16 @@
         <v>83</v>
       </c>
       <c r="C78" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D78" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="F78" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="G78" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2693,16 +2954,16 @@
         <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D79" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="F79" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="G79" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2710,16 +2971,16 @@
         <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D80" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="F80" t="s">
-        <v>325</v>
+        <v>390</v>
       </c>
       <c r="G80" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2727,16 +2988,16 @@
         <v>86</v>
       </c>
       <c r="C81" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D81" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="F81" t="s">
-        <v>326</v>
+        <v>391</v>
       </c>
       <c r="G81" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2744,16 +3005,16 @@
         <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D82" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="F82" t="s">
-        <v>327</v>
+        <v>392</v>
       </c>
       <c r="G82" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2761,16 +3022,16 @@
         <v>88</v>
       </c>
       <c r="C83" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D83" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="F83" t="s">
-        <v>328</v>
+        <v>393</v>
       </c>
       <c r="G83" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2778,16 +3039,16 @@
         <v>89</v>
       </c>
       <c r="C84" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D84" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="F84" t="s">
-        <v>329</v>
+        <v>394</v>
       </c>
       <c r="G84" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2795,16 +3056,16 @@
         <v>90</v>
       </c>
       <c r="C85" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D85" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="F85" t="s">
-        <v>330</v>
+        <v>395</v>
       </c>
       <c r="G85" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2812,16 +3073,16 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D86" t="s">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="F86" t="s">
-        <v>331</v>
+        <v>396</v>
       </c>
       <c r="G86" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2829,16 +3090,16 @@
         <v>92</v>
       </c>
       <c r="C87" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D87" t="s">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="F87" t="s">
-        <v>332</v>
+        <v>397</v>
       </c>
       <c r="G87" t="s">
-        <v>334</v>
+        <v>421</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2846,16 +3107,407 @@
         <v>93</v>
       </c>
       <c r="C88" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D88" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="F88" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="G88" t="s">
-        <v>334</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>94</v>
+      </c>
+      <c r="C89" t="s">
+        <v>204</v>
+      </c>
+      <c r="D89" t="s">
+        <v>293</v>
+      </c>
+      <c r="F89" t="s">
+        <v>399</v>
+      </c>
+      <c r="G89" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" t="s">
+        <v>205</v>
+      </c>
+      <c r="D90" t="s">
+        <v>294</v>
+      </c>
+      <c r="F90" t="s">
+        <v>400</v>
+      </c>
+      <c r="G90" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" t="s">
+        <v>206</v>
+      </c>
+      <c r="D91" t="s">
+        <v>295</v>
+      </c>
+      <c r="F91" t="s">
+        <v>401</v>
+      </c>
+      <c r="G91" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" t="s">
+        <v>207</v>
+      </c>
+      <c r="D92" t="s">
+        <v>230</v>
+      </c>
+      <c r="F92" t="s">
+        <v>338</v>
+      </c>
+      <c r="G92" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93" t="s">
+        <v>208</v>
+      </c>
+      <c r="D93" t="s">
+        <v>296</v>
+      </c>
+      <c r="F93" t="s">
+        <v>402</v>
+      </c>
+      <c r="G93" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>99</v>
+      </c>
+      <c r="C94" t="s">
+        <v>209</v>
+      </c>
+      <c r="D94" t="s">
+        <v>297</v>
+      </c>
+      <c r="F94" t="s">
+        <v>403</v>
+      </c>
+      <c r="G94" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>100</v>
+      </c>
+      <c r="C95" t="s">
+        <v>210</v>
+      </c>
+      <c r="D95" t="s">
+        <v>298</v>
+      </c>
+      <c r="F95" t="s">
+        <v>404</v>
+      </c>
+      <c r="G95" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>101</v>
+      </c>
+      <c r="C96" t="s">
+        <v>211</v>
+      </c>
+      <c r="D96" t="s">
+        <v>299</v>
+      </c>
+      <c r="F96" t="s">
+        <v>405</v>
+      </c>
+      <c r="G96" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" t="s">
+        <v>212</v>
+      </c>
+      <c r="D97" t="s">
+        <v>300</v>
+      </c>
+      <c r="F97" t="s">
+        <v>406</v>
+      </c>
+      <c r="G97" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>103</v>
+      </c>
+      <c r="C98" t="s">
+        <v>213</v>
+      </c>
+      <c r="D98" t="s">
+        <v>230</v>
+      </c>
+      <c r="F98" t="s">
+        <v>407</v>
+      </c>
+      <c r="G98" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>104</v>
+      </c>
+      <c r="C99" t="s">
+        <v>214</v>
+      </c>
+      <c r="D99" t="s">
+        <v>241</v>
+      </c>
+      <c r="F99" t="s">
+        <v>408</v>
+      </c>
+      <c r="G99" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>105</v>
+      </c>
+      <c r="C100" t="s">
+        <v>215</v>
+      </c>
+      <c r="D100" t="s">
+        <v>301</v>
+      </c>
+      <c r="F100" t="s">
+        <v>409</v>
+      </c>
+      <c r="G100" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101" t="s">
+        <v>216</v>
+      </c>
+      <c r="D101" t="s">
+        <v>302</v>
+      </c>
+      <c r="F101" t="s">
+        <v>410</v>
+      </c>
+      <c r="G101" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>107</v>
+      </c>
+      <c r="C102" t="s">
+        <v>217</v>
+      </c>
+      <c r="D102" t="s">
+        <v>303</v>
+      </c>
+      <c r="F102" t="s">
+        <v>411</v>
+      </c>
+      <c r="G102" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>108</v>
+      </c>
+      <c r="C103" t="s">
+        <v>218</v>
+      </c>
+      <c r="D103" t="s">
+        <v>304</v>
+      </c>
+      <c r="F103" t="s">
+        <v>412</v>
+      </c>
+      <c r="G103" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>109</v>
+      </c>
+      <c r="C104" t="s">
+        <v>219</v>
+      </c>
+      <c r="D104" t="s">
+        <v>305</v>
+      </c>
+      <c r="F104" t="s">
+        <v>413</v>
+      </c>
+      <c r="G104" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>110</v>
+      </c>
+      <c r="C105" t="s">
+        <v>220</v>
+      </c>
+      <c r="D105" t="s">
+        <v>230</v>
+      </c>
+      <c r="F105" t="s">
+        <v>414</v>
+      </c>
+      <c r="G105" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>111</v>
+      </c>
+      <c r="C106" t="s">
+        <v>221</v>
+      </c>
+      <c r="D106" t="s">
+        <v>306</v>
+      </c>
+      <c r="F106" t="s">
+        <v>415</v>
+      </c>
+      <c r="G106" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>112</v>
+      </c>
+      <c r="C107" t="s">
+        <v>222</v>
+      </c>
+      <c r="D107" t="s">
+        <v>307</v>
+      </c>
+      <c r="F107" t="s">
+        <v>416</v>
+      </c>
+      <c r="G107" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>113</v>
+      </c>
+      <c r="C108" t="s">
+        <v>223</v>
+      </c>
+      <c r="D108" t="s">
+        <v>308</v>
+      </c>
+      <c r="F108" t="s">
+        <v>417</v>
+      </c>
+      <c r="G108" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>114</v>
+      </c>
+      <c r="C109" t="s">
+        <v>224</v>
+      </c>
+      <c r="D109" t="s">
+        <v>309</v>
+      </c>
+      <c r="F109" t="s">
+        <v>418</v>
+      </c>
+      <c r="G109" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>115</v>
+      </c>
+      <c r="C110" t="s">
+        <v>225</v>
+      </c>
+      <c r="D110" t="s">
+        <v>310</v>
+      </c>
+      <c r="F110" t="s">
+        <v>419</v>
+      </c>
+      <c r="G110" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>116</v>
+      </c>
+      <c r="C111" t="s">
+        <v>226</v>
+      </c>
+      <c r="D111" t="s">
+        <v>311</v>
+      </c>
+      <c r="F111" t="s">
+        <v>420</v>
+      </c>
+      <c r="G111" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
